--- a/РАБОЧИЙ СТОЛ/ПРОБЛЕМЫ/Сыр проблема/дв 21,07,26 бррсч ост сыр.xlsx
+++ b/РАБОЧИЙ СТОЛ/ПРОБЛЕМЫ/Сыр проблема/дв 21,07,26 бррсч ост сыр.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\ПРОБЛЕМЫ\Сыр проблема\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\ПРОБЛЕМЫ\Сыр проблема\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C30A81E-D460-431E-A7F4-F62EB1414A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297BC4CA-4455-4E42-8346-FC7BB86824E4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,15 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AD$60</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -364,7 +372,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -396,6 +404,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,7 +449,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -452,6 +466,7 @@
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -773,7 +788,8 @@
     <col min="21" max="28" width="6" customWidth="1"/>
     <col min="29" max="29" width="44" customWidth="1"/>
     <col min="30" max="30" width="7" customWidth="1"/>
-    <col min="31" max="50" width="3" customWidth="1"/>
+    <col min="31" max="31" width="4.140625" customWidth="1"/>
+    <col min="32" max="50" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.25">
@@ -1585,7 +1601,7 @@
       <c r="AX9" s="1"/>
     </row>
     <row r="10" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="16" t="s">
         <v>38</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1664,7 +1680,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AE10" s="1"/>
+      <c r="AE10" s="1">
+        <v>3</v>
+      </c>
       <c r="AF10" s="1"/>
       <c r="AG10" s="1"/>
       <c r="AH10" s="1"/>
@@ -3141,7 +3159,7 @@
       <c r="AX24" s="1"/>
     </row>
     <row r="25" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="16" t="s">
         <v>55</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -3220,7 +3238,9 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AE25" s="1"/>
+      <c r="AE25" s="1">
+        <v>4</v>
+      </c>
       <c r="AF25" s="1"/>
       <c r="AG25" s="1"/>
       <c r="AH25" s="1"/>
@@ -5397,7 +5417,7 @@
       <c r="AX46" s="1"/>
     </row>
     <row r="47" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="16" t="s">
         <v>77</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -5476,7 +5496,9 @@
         <f>G47*Q47</f>
         <v>0</v>
       </c>
-      <c r="AE47" s="1"/>
+      <c r="AE47" s="1">
+        <v>16</v>
+      </c>
       <c r="AF47" s="1"/>
       <c r="AG47" s="1"/>
       <c r="AH47" s="1"/>
@@ -5498,7 +5520,7 @@
       <c r="AX47" s="1"/>
     </row>
     <row r="48" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="16" t="s">
         <v>78</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -5577,7 +5599,9 @@
         <f>G48*Q48</f>
         <v>0</v>
       </c>
-      <c r="AE48" s="1"/>
+      <c r="AE48" s="1">
+        <v>29</v>
+      </c>
       <c r="AF48" s="1"/>
       <c r="AG48" s="1"/>
       <c r="AH48" s="1"/>

--- a/РАБОЧИЙ СТОЛ/ПРОБЛЕМЫ/Сыр проблема/дв 21,07,26 бррсч ост сыр.xlsx
+++ b/РАБОЧИЙ СТОЛ/ПРОБЛЕМЫ/Сыр проблема/дв 21,07,26 бррсч ост сыр.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\ПРОБЛЕМЫ\Сыр проблема\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\ПРОБЛЕМЫ\Сыр проблема\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297BC4CA-4455-4E42-8346-FC7BB86824E4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6085D8D-A210-46CE-8090-8BDCBEFE5A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,15 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AD$60</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
